--- a/artfynd/A 17006-2026 artfynd.xlsx
+++ b/artfynd/A 17006-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>86851087</v>
+        <v>86851080</v>
       </c>
       <c r="B2" t="n">
-        <v>98264</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616688</v>
+        <v>616612</v>
       </c>
       <c r="R2" t="n">
-        <v>6872550</v>
+        <v>6872572</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>86851083</v>
+        <v>86851092</v>
       </c>
       <c r="B3" t="n">
-        <v>98264</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616621</v>
+        <v>616790</v>
       </c>
       <c r="R3" t="n">
-        <v>6872586</v>
+        <v>6872589</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Höna</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>86851091</v>
+        <v>86851067</v>
       </c>
       <c r="B4" t="n">
-        <v>98264</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616755</v>
+        <v>616615</v>
       </c>
       <c r="R4" t="n">
-        <v>6872698</v>
+        <v>6872563</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>86851084</v>
+        <v>86851068</v>
       </c>
       <c r="B5" t="n">
-        <v>98264</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616636</v>
+        <v>616631</v>
       </c>
       <c r="R5" t="n">
-        <v>6872601</v>
+        <v>6872563</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,6 +1070,879 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>86851069</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Längs E4 mellan Kongberget och Gnarp, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>616642</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6872564</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sofia Lundman, Oskar Wallströmer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>86851070</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Längs E4 mellan Kongberget och Gnarp, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>616659</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6872563</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sofia Lundman, Oskar Wallströmer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>86851081</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Längs E4 mellan Kongberget och Gnarp, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>616612</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6872572</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sofia Lundman, Oskar Wallströmer</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>86851082</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Längs E4 mellan Kongberget och Gnarp, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>616618</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6872574</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sofia Lundman, Oskar Wallströmer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>86851083</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Längs E4 mellan Kongberget och Gnarp, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>616621</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6872586</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sofia Lundman, Oskar Wallströmer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>86851084</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Längs E4 mellan Kongberget och Gnarp, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>616636</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6872601</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sofia Lundman, Oskar Wallströmer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>86851085</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Längs E4 mellan Kongberget och Gnarp, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>616661</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6872587</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sofia Lundman, Oskar Wallströmer</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>86851087</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Längs E4 mellan Kongberget och Gnarp, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>616688</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6872550</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sofia Lundman, Oskar Wallströmer</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>86851091</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Längs E4 mellan Kongberget och Gnarp, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>616755</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6872698</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sofia Lundman, Oskar Wallströmer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17006-2026 artfynd.xlsx
+++ b/artfynd/A 17006-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86851080</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86851092</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86851067</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86851068</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86851069</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86851070</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86851081</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86851082</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86851083</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86851084</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1749,6 +1804,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86851085</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86851087</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1943,8 +2008,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86851091</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>